--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.63291003281306</v>
+        <v>12.29034788033212</v>
       </c>
       <c r="D2" t="n">
-        <v>74.91078630761476</v>
+        <v>12.1730027749874</v>
       </c>
       <c r="E2" t="n">
-        <v>18.27617344365627</v>
+        <v>2.969878184594144</v>
       </c>
       <c r="F2" t="n">
-        <v>17.96219617889932</v>
+        <v>2.918856879071139</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.69038701840662</v>
+        <v>3.687187890491077</v>
       </c>
       <c r="D3" t="n">
-        <v>22.94935921233544</v>
+        <v>3.729270872004509</v>
       </c>
       <c r="E3" t="n">
-        <v>18.27617344365627</v>
+        <v>2.969878184594144</v>
       </c>
       <c r="F3" t="n">
-        <v>17.96219617889932</v>
+        <v>2.918856879071139</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.85253875901857</v>
+        <v>6.151037548340518</v>
       </c>
       <c r="D4" t="n">
-        <v>37.87535024570168</v>
+        <v>6.154744414926522</v>
       </c>
       <c r="E4" t="n">
-        <v>18.27617344365627</v>
+        <v>2.969878184594144</v>
       </c>
       <c r="F4" t="n">
-        <v>17.96219617889932</v>
+        <v>2.918856879071139</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.53803310820879</v>
+        <v>8.699930380083929</v>
       </c>
       <c r="D5" t="n">
-        <v>54.24965116134783</v>
+        <v>8.815568313719023</v>
       </c>
       <c r="E5" t="n">
-        <v>18.27617344365627</v>
+        <v>2.969878184594144</v>
       </c>
       <c r="F5" t="n">
-        <v>17.96219617889932</v>
+        <v>2.918856879071139</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.50541751992988</v>
+        <v>5.607130346988606</v>
       </c>
       <c r="D6" t="n">
-        <v>35.20169085488638</v>
+        <v>5.720274763919037</v>
       </c>
       <c r="E6" t="n">
-        <v>18.27617344365627</v>
+        <v>2.969878184594144</v>
       </c>
       <c r="F6" t="n">
-        <v>17.96219617889932</v>
+        <v>2.918856879071139</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
